--- a/survey_templates/017_sleeping_habits_survey--survey_templates.xlsx
+++ b/survey_templates/017_sleeping_habits_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_do_you_do_at_night</t>
+          <t>1. What time do you typically go to sleep?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sleep_time</t>
+          <t>sleeping_habits_survey_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_time_do_you_go_to_sleep</t>
+          <t>2. What time do you wake up?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wake_time</t>
+          <t>sleeping_habits_survey_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_time_do_you_wake_up</t>
+          <t>3. Do you have any sleep patterns?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sleep_patterns</t>
+          <t>sleeping_habits_survey_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_do_you_sleep</t>
+          <t>4. How do you wake up?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wake_up_patterns</t>
+          <t>sleeping_habits_survey_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_do_you_wake_up</t>
+          <t>5. How much time do you spend exercising per day?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exercise_time</t>
+          <t>sleeping_habits_survey_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>how_much_time_do_you_spend_exercising</t>
+          <t>6. How much screen time do you spend per day?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>screen_time</t>
+          <t>sleeping_habits_survey_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>how_much_screen_time_do_you_spend</t>
+          <t>7. How much time do you spend studying per day?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>study_time</t>
+          <t>sleeping_habits_survey_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>how_much_time_do_you_spend_studying</t>
+          <t>8. What is the quality of your sleep?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sleep_quality</t>
+          <t>sleeping_habits_survey_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_is_the_quality_of_your_sleep</t>
+          <t>9. How often do you sleep at night?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sleep_frequency</t>
+          <t>sleeping_habits_survey_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>how_ofently_do_you_sleep</t>
+          <t>10. Where do you sleep?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sleep_location</t>
+          <t>sleeping_habits_survey_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>where_do_you_sleep</t>
+          <t>11. Have you been woken up by anything recently?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sleep_enviro</t>
+          <t>sleeping_habits_survey_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_environment_do_you_sleep_in</t>
+          <t>12. What was it that woke you up?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sleep_disturbance</t>
+          <t>sleeping_habits_survey_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>have_you_been_woken_up_by_something</t>
+          <t>13. How often do you get woken up by disturbances?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source</t>
+          <t>sleeping_habits_survey_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_woke_you_up</t>
+          <t>14. Describe what happened.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency</t>
+          <t>sleeping_habits_survey_page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>how_ofentally_did_it_happen</t>
+          <t>15. What was the impact of the disturbance on your sleep?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_description</t>
+          <t>sleeping_habits_survey_page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>describe_the_event</t>
+          <t>16. What type of disturbance was it?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sleep_quality_source</t>
+          <t>sleeping_habits_survey_page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_was_the_impact_of_the_disturbance</t>
+          <t>17. Describe other disturbances.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_type</t>
+          <t>sleeping_habits_survey_page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>what_type_of_disturbance_was_it</t>
+          <t>18. How often do other disturbances happen?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>describe</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_frequency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>how_ofentally_did_it_happen</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_description_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>describe_what_happened</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_description_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>describe_what_happened</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_description_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>describe_what_happened</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_description_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>describe_what_happened</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sleep_patterns_choices</t>
+          <t>sleeping_habits_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sleep_patterns_choices</t>
+          <t>sleeping_habits_survey_page_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wake_up_patterns_choices</t>
+          <t>sleeping_habits_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wake_up_patterns_choices</t>
+          <t>sleeping_habits_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wake_up_patterns_choices</t>
+          <t>sleeping_habits_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wake_up_patterns_choices</t>
+          <t>sleeping_habits_survey_page_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>study_time_choices</t>
+          <t>sleeping_habits_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>study_time_choices</t>
+          <t>sleeping_habits_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>study_time_choices</t>
+          <t>sleeping_habits_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>study_time_choices</t>
+          <t>sleeping_habits_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1135,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>study_time_choices</t>
+          <t>sleeping_habits_survey_page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>sleeping_habits_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sleep_quality_choices</t>
+          <t>sleeping_habits_survey_page_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1203,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1220,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1271,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sleep_frequency_choices</t>
+          <t>sleeping_habits_survey_page_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sleep_location_choices</t>
+          <t>sleeping_habits_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1305,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sleep_location_choices</t>
+          <t>sleeping_habits_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,287 +1322,253 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_choices</t>
+          <t>sleeping_habits_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_1_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 1 time</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_choices</t>
+          <t>sleeping_habits_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1-2_times</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1-2 times</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency_choices</t>
+          <t>sleeping_habits_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>less_than_1_time</t>
+          <t>2-5_times</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Less than 1 time</t>
+          <t>2-5 times</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency_choices</t>
+          <t>sleeping_habits_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1-2_times</t>
+          <t>5-10_times</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1-2 times</t>
+          <t>5-10 times</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency_choices</t>
+          <t>sleeping_habits_survey_page_13_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2-5_times</t>
+          <t>more_than_10_times</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2-5 times</t>
+          <t>More than 10 times</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency_choices</t>
+          <t>sleeping_habits_survey_page_15_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5-10_times</t>
+          <t>not_impactful</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5-10 times</t>
+          <t>Not impactful</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sleep_disturbance_frequency_choices</t>
+          <t>sleeping_habits_survey_page_15_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>more_than_10_times</t>
+          <t>somewhat_impactful</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>More than 10 times</t>
+          <t>Somewhat impactful</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sleep_quality_source_choices</t>
+          <t>sleeping_habits_survey_page_15_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>not_impactful</t>
+          <t>very_impactful</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Not impactful</t>
+          <t>Very impactful</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sleep_quality_source_choices</t>
+          <t>sleeping_habits_survey_page_16_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>somewhat_impactful</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Somewhat impactful</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sleep_quality_source_choices</t>
+          <t>sleeping_habits_survey_page_16_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>very_impactful</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Very impactful</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_type_choices</t>
+          <t>sleeping_habits_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_1_time</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 1 time</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_type_choices</t>
+          <t>sleeping_habits_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1-2_times</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1-2 times</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_other_frequency_choices</t>
+          <t>sleeping_habits_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>less_than_1_time</t>
+          <t>2-5_times</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Less than 1 time</t>
+          <t>2-5 times</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_other_frequency_choices</t>
+          <t>sleeping_habits_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1-2_times</t>
+          <t>5-10_times</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1-2 times</t>
+          <t>5-10 times</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sleep_disturbance_source_other_frequency_choices</t>
+          <t>sleeping_habits_survey_page_18_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2-5_times</t>
+          <t>more_than_10_times</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>2-5 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>5-10_times</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>5-10 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sleep_disturbance_source_other_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>more_than_10_times</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
         <is>
           <t>More than 10 times</t>
         </is>
